--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1613,22 +1613,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>22</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>

--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1671,22 +1671,62 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U. Catolica</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" t="n">
+        <v>15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>

--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1729,22 +1729,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>06/09/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>U. Calera</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>

--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1787,22 +1787,62 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A. Italiano</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" t="n">
+        <v>11</v>
+      </c>
+      <c r="O24" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>

--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1845,22 +1845,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M25" t="n">
+        <v>19</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>

--- a/new-stats/o-higgins-fc.xlsx
+++ b/new-stats/o-higgins-fc.xlsx
@@ -1903,22 +1903,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M26" t="n">
+        <v>22</v>
+      </c>
+      <c r="N26" t="n">
+        <v>18</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
